--- a/AAII_Financials/Quarterly/TCEHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCEHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>TCEHY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2126,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30463100</v>
+      </c>
+      <c r="E41" s="3">
         <v>31572800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20164800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22471900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25413500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28285400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18155500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20738200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21124700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22300800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24301600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20074600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19255500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22321100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22725000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>37094300</v>
+      </c>
+      <c r="E42" s="3">
         <v>35077700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>40248100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>36895900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27693000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>23797300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28207600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30629400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>29619400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>35734400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>29169100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>29605400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>28691600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27070800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>19430600</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14366100</v>
+      </c>
+      <c r="E43" s="3">
         <v>8425800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13593700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7354300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12036500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6795400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11267400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6748300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11557300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7258800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11320600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6486200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10991000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6610700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10347200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E44" s="3">
         <v>84400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>75800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>77300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>60700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>58800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>60300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1400400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>603700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>146100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>64300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>229700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>297100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>293300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>338300</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11477700</v>
+      </c>
+      <c r="E45" s="3">
         <v>17532100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7447800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14470200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7409900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14058400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7455700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14703100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5615600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12154400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5439600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12512400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5299100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12169800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26505100</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>97665800</v>
+      </c>
+      <c r="E46" s="3">
         <v>93794200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85133800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81772200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>76146300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73483800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67978200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>74726100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>71783200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>78070100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>73114300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>69347500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>67621200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>69029700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>82060700</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>135156800</v>
+      </c>
+      <c r="E47" s="3">
         <v>132984700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>140514000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>145245500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>142000100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>131201700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>120888200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>119322000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107762600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>101964100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>101339600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>95808500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>98788000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>104175300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>98499400</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32935200</v>
+      </c>
+      <c r="E48" s="3">
         <v>27363600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25297700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23413400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20932300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16821100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15093100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14281400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12310300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11942700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12308600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11489300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11359400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12062400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12429800</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33568600</v>
+      </c>
+      <c r="E49" s="3">
         <v>32059900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32645800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>33002000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>33295900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>31774100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>30037100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28809300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27673400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>27919100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27486800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26508600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26160900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26223600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>26075500</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13452600</v>
+      </c>
+      <c r="E52" s="3">
         <v>6906800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3281100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3583400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3939900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7008800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5662500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4096200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3427700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3930800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3573900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3981600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3536000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5068100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4714200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>317894500</v>
+      </c>
+      <c r="E54" s="3">
         <v>297415000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>291516900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>291222600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>281039400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>264353300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244002000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>245684900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>227740900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>228055800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>222432400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>211226200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>212002100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>220870800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>228807500</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25847800</v>
+      </c>
+      <c r="E57" s="3">
         <v>20550900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17317700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18084800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18216700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17293200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16263900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20338600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16682500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15583400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14236300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15338800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13802900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14895000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13394000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13513000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8728800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8370400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9572400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10728100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8119500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9194000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8090800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8926900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10333200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8722700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9075700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9129000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4665500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4114700</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29348700</v>
+      </c>
+      <c r="E59" s="3">
         <v>35634900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25236900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31989000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26394000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>30209600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22300800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29009300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22402500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27257400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19863500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24485100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19865000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24968400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39245600</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75886400</v>
+      </c>
+      <c r="E60" s="3">
         <v>65803300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59011600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>60292400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>60737500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56327700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54377800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58133400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53368800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>53813900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>49663200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>49659300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48103900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45186600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>62953700</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55947000</v>
+      </c>
+      <c r="E61" s="3">
         <v>50063100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>49733100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47919300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46851100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47643400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39868500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>41757500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41214300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>41464900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43631700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42034200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42934100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48046100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>47955800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2451900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2092200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1919100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2403100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2572400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2249800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1973400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2869900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2889700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2881800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2954500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2926400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2587200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2612100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2122700</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>137922700</v>
+      </c>
+      <c r="E66" s="3">
         <v>121750700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>114080000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>114164100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>113132800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>109604100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>99614900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>105902100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100094000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>101088300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>99220800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97345100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>96064300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>98386000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>115303500</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>157043200</v>
+      </c>
+      <c r="E72" s="3">
         <v>153840900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>145907400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>135592100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>128450300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>126961600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>123357100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>122862500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>115874400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>118691900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>115758800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>107922600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>103588700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>108340400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>103229100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>167214300</v>
+      </c>
+      <c r="E76" s="3">
         <v>163489400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>165010900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164636500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>155593300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>143382300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>133379200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>130099900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>118438500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>117524700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>114032200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>105324900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107317100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>113329500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>104591900</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="E83" s="3">
         <v>935700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>869700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>958900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>902600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>919700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>819100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>871600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>911700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>971300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>810600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>981400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1084000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1154900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>990100</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7759700</v>
+      </c>
+      <c r="E89" s="3">
         <v>14694100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9504000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11983400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10382200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10595900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7404500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11122200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7445800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10020100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7608900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8911700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5610100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9069000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5161900</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8629000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5364300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3991200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1967600</v>
       </c>
-      <c r="G91" s="3">
-        <v>-3148900</v>
-      </c>
       <c r="H91" s="3">
+        <v>-2524100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-3786400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3116100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3939000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>248700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1988600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-654200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1372400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-268100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-642100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1495700</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9445900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1531000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8266300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10606100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5989600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4065200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5883500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4817700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3092800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9407100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1128800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4444900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2692200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9491500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2658800</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>6123400</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>481900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5239500</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>411100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3971300</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>243800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2893300</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
         <v>1877900</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>389800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1756700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3775400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4303400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7667600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3420100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3447500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7348900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11596400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2148200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2787700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3455000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5233500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>52300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2997200</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E101" s="3">
         <v>72500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>152500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-102200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-29400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-47800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-75800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>429200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-126400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>481300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>681700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-244900</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1595800</v>
+      </c>
+      <c r="E102" s="3">
         <v>11124300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2708000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3100800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3237900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10023300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1774100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1146600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1033700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1564600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3644700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>935900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1886400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-496600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-498500</v>
       </c>
     </row>
